--- a/tables/datas/__beans__.xlsx
+++ b/tables/datas/__beans__.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.625" customWidth="1" style="4" min="2" max="2"/>
@@ -756,334 +756,387 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>common.MonsterAttr</t>
+        </is>
+      </c>
+      <c r="F11" s="0" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="G11" s="0" t="inlineStr">
+        <is>
+          <t>怪物属性项</t>
+        </is>
+      </c>
+      <c r="I11" s="0" t="inlineStr">
+        <is>
+          <t>c,s,e</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>attr_key</t>
+        </is>
+      </c>
+      <c r="L11" s="0" t="inlineStr">
+        <is>
+          <t>common.EMonsterAttr</t>
+        </is>
+      </c>
+      <c r="N11" s="0" t="inlineStr">
+        <is>
+          <t>属性键</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
-      <c r="B12" s="0" t="inlineStr">
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>attr_value</t>
+        </is>
+      </c>
+      <c r="L12" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N12" s="0" t="inlineStr">
+        <is>
+          <t>属性值</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="0" t="inlineStr">
         <is>
           <t>test.Shape</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="0" t="inlineStr">
+    <row r="16">
+      <c r="B16" s="0" t="inlineStr">
         <is>
           <t>test.Circle</t>
         </is>
       </c>
-      <c r="C13" s="0" t="inlineStr">
+      <c r="C16" s="0" t="inlineStr">
         <is>
           <t>Shape</t>
         </is>
       </c>
-      <c r="E13" s="0" t="inlineStr">
+      <c r="E16" s="0" t="inlineStr">
         <is>
           <t>圆</t>
         </is>
       </c>
-      <c r="G13" s="0" t="inlineStr">
+      <c r="G16" s="0" t="inlineStr">
         <is>
           <t>圆</t>
         </is>
       </c>
-      <c r="J13" s="0" t="inlineStr">
+      <c r="J16" s="0" t="inlineStr">
         <is>
           <t>radius</t>
         </is>
       </c>
-      <c r="L13" s="0" t="inlineStr">
+      <c r="L16" s="0" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="N13" s="0" t="inlineStr">
+      <c r="N16" s="0" t="inlineStr">
         <is>
           <t>半径</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="0" t="inlineStr">
+    <row r="17">
+      <c r="B17" s="0" t="inlineStr">
         <is>
           <t>test2.Rectangle</t>
         </is>
       </c>
-      <c r="C14" s="0" t="inlineStr">
+      <c r="C17" s="0" t="inlineStr">
         <is>
           <t>test.Shape</t>
         </is>
       </c>
-      <c r="E14" s="0" t="inlineStr">
+      <c r="E17" s="0" t="inlineStr">
         <is>
           <t>矩形</t>
         </is>
       </c>
-      <c r="G14" s="0" t="inlineStr">
+      <c r="G17" s="0" t="inlineStr">
         <is>
           <t>矩形</t>
         </is>
       </c>
-      <c r="J14" s="0" t="inlineStr">
+      <c r="J17" s="0" t="inlineStr">
         <is>
           <t>width</t>
         </is>
       </c>
-      <c r="L14" s="0" t="inlineStr">
+      <c r="L17" s="0" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="N14" s="0" t="inlineStr">
+      <c r="N17" s="0" t="inlineStr">
         <is>
           <t>宽度</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="J15" s="0" t="inlineStr">
+    <row r="18">
+      <c r="J18" s="0" t="inlineStr">
         <is>
           <t>height</t>
         </is>
       </c>
-      <c r="L15" s="0" t="inlineStr">
+      <c r="L18" s="0" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="N15" s="0" t="inlineStr">
+      <c r="N18" s="0" t="inlineStr">
         <is>
           <t>高度</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="0" t="inlineStr">
         <is>
           <t>AccountConfig</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G19" s="0" t="inlineStr">
         <is>
           <t>账号配置数据结构</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I19" s="0" t="inlineStr">
         <is>
           <t>c,s,e</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J19" s="0" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
+      <c r="L19" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N19" s="0" t="inlineStr">
         <is>
           <t>配置ID</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="J17" t="inlineStr">
+    <row r="20">
+      <c r="J20" s="0" t="inlineStr">
         <is>
           <t>max_role_count</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
+      <c r="L20" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N20" s="0" t="inlineStr">
         <is>
           <t>最大角色数</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="J18" t="inlineStr">
+    <row r="21">
+      <c r="J21" s="0" t="inlineStr">
         <is>
           <t>role_name_min_len</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
+      <c r="L21" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N21" s="0" t="inlineStr">
         <is>
           <t>角色名最小长度</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="J19" t="inlineStr">
+    <row r="22">
+      <c r="J22" s="0" t="inlineStr">
         <is>
           <t>role_name_max_len</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
+      <c r="L22" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N22" s="0" t="inlineStr">
         <is>
           <t>角色名最大长度</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="J20" t="inlineStr">
+    <row r="23">
+      <c r="J23" s="0" t="inlineStr">
         <is>
           <t>init_level</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
+      <c r="L23" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N23" s="0" t="inlineStr">
         <is>
           <t>初始等级</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="J21" t="inlineStr">
+    <row r="24">
+      <c r="J24" s="0" t="inlineStr">
         <is>
           <t>init_gold</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
+      <c r="L24" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N24" s="0" t="inlineStr">
         <is>
           <t>初始金币</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="J22" t="inlineStr">
+    <row r="25">
+      <c r="J25" s="0" t="inlineStr">
         <is>
           <t>init_diamond</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
+      <c r="L25" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N25" s="0" t="inlineStr">
         <is>
           <t>初始钻石</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="J23" t="inlineStr">
+    <row r="26">
+      <c r="J26" s="0" t="inlineStr">
         <is>
           <t>init_avatar_id</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
+      <c r="L26" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N26" s="0" t="inlineStr">
         <is>
           <t>初始头像ID</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="B25" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="0" t="inlineStr">
         <is>
           <t>RoleInitConfig</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G28" s="0" t="inlineStr">
         <is>
           <t>角色初始配置</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I28" s="0" t="inlineStr">
         <is>
           <t>c,s,e</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J28" s="0" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
+      <c r="L28" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N28" s="0" t="inlineStr">
         <is>
           <t>配置ID</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="J26" t="inlineStr">
+    <row r="29">
+      <c r="J29" s="0" t="inlineStr">
         <is>
           <t>init_items</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L29" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N29" s="0" t="inlineStr">
         <is>
           <t>初始道具(itemId:count,itemId:count)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="J27" t="inlineStr">
+    <row r="30">
+      <c r="J30" s="0" t="inlineStr">
         <is>
           <t>init_tasks</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="L30" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N30" s="0" t="inlineStr">
         <is>
           <t>初始任务(taskId,taskId)</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="J28" t="inlineStr">
+    <row r="31">
+      <c r="J31" s="0" t="inlineStr">
         <is>
           <t>init_guide_step</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
+      <c r="L31" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N31" s="0" t="inlineStr">
         <is>
           <t>初始引导步骤</t>
         </is>

--- a/tables/datas/__beans__.xlsx
+++ b/tables/datas/__beans__.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.625" customWidth="1" style="4" min="2" max="2"/>
@@ -1142,6 +1142,77 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="0" t="inlineStr">
+        <is>
+          <t>common.CombatActionBean</t>
+        </is>
+      </c>
+      <c r="B32" s="0" t="inlineStr">
+        <is>
+          <t>common.CombatActionBean</t>
+        </is>
+      </c>
+      <c r="F32" s="0" t="inlineStr">
+        <is>
+          <t>,</t>
+        </is>
+      </c>
+      <c r="G32" s="0" t="inlineStr">
+        <is>
+          <t>战斗动作配置</t>
+        </is>
+      </c>
+      <c r="J32" s="0" t="inlineStr">
+        <is>
+          <t>action_type</t>
+        </is>
+      </c>
+      <c r="L32" s="0" t="inlineStr">
+        <is>
+          <t>common.ECombatActionType</t>
+        </is>
+      </c>
+      <c r="N32" s="0" t="inlineStr">
+        <is>
+          <t>动作类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="J33" s="0" t="inlineStr">
+        <is>
+          <t>damage_type</t>
+        </is>
+      </c>
+      <c r="L33" s="0" t="inlineStr">
+        <is>
+          <t>common.EDamageType</t>
+        </is>
+      </c>
+      <c r="N33" s="0" t="inlineStr">
+        <is>
+          <t>伤害类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="J34" s="0" t="inlineStr">
+        <is>
+          <t>coefficient</t>
+        </is>
+      </c>
+      <c r="L34" s="0" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="N34" s="0" t="inlineStr">
+        <is>
+          <t>系数</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J1:P1"/>

--- a/tables/datas/__beans__.xlsx
+++ b/tables/datas/__beans__.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P34"/>
+  <dimension ref="A1:P96"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.625" customWidth="1" style="4" min="2" max="2"/>
@@ -1213,6 +1213,1205 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="J35" s="0" t="inlineStr">
+        <is>
+          <t>buff_id</t>
+        </is>
+      </c>
+      <c r="L35" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N35" s="0" t="inlineStr">
+        <is>
+          <t>Buff配置ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="0" t="inlineStr">
+        <is>
+          <t>common.BuffEffectBean</t>
+        </is>
+      </c>
+      <c r="F36" s="0" t="inlineStr">
+        <is>
+          <t>,</t>
+        </is>
+      </c>
+      <c r="G36" s="0" t="inlineStr">
+        <is>
+          <t>Buff效果Bean</t>
+        </is>
+      </c>
+      <c r="J36" s="0" t="inlineStr">
+        <is>
+          <t>trigger</t>
+        </is>
+      </c>
+      <c r="L36" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N36" s="0" t="inlineStr">
+        <is>
+          <t>触发时机: OnTick/OnApply/OnRemove</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="J37" s="0" t="inlineStr">
+        <is>
+          <t>action_type</t>
+        </is>
+      </c>
+      <c r="L37" s="0" t="inlineStr">
+        <is>
+          <t>common.ECombatActionType</t>
+        </is>
+      </c>
+      <c r="N37" s="0" t="inlineStr">
+        <is>
+          <t>动作类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="J38" s="0" t="inlineStr">
+        <is>
+          <t>damage_type</t>
+        </is>
+      </c>
+      <c r="L38" s="0" t="inlineStr">
+        <is>
+          <t>common.EDamageType</t>
+        </is>
+      </c>
+      <c r="N38" s="0" t="inlineStr">
+        <is>
+          <t>伤害类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="J39" s="0" t="inlineStr">
+        <is>
+          <t>coefficient</t>
+        </is>
+      </c>
+      <c r="L39" s="0" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="N39" s="0" t="inlineStr">
+        <is>
+          <t>系数</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="J40" s="0" t="inlineStr">
+        <is>
+          <t>buff_id</t>
+        </is>
+      </c>
+      <c r="L40" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N40" s="0" t="inlineStr">
+        <is>
+          <t>嵌套Buff ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="0" t="inlineStr">
+        <is>
+          <t>common.BuffAttrModifierBean</t>
+        </is>
+      </c>
+      <c r="F41" s="0" t="inlineStr">
+        <is>
+          <t>,</t>
+        </is>
+      </c>
+      <c r="G41" s="0" t="inlineStr">
+        <is>
+          <t>Buff属性修正Bean</t>
+        </is>
+      </c>
+      <c r="J41" s="0" t="inlineStr">
+        <is>
+          <t>attr</t>
+        </is>
+      </c>
+      <c r="L41" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N41" s="0" t="inlineStr">
+        <is>
+          <t>属性名: patk/matk/pdef/mdef等</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="J42" s="0" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="L42" s="0" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="N42" s="0" t="inlineStr">
+        <is>
+          <t>修正值</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="J43" s="0" t="inlineStr">
+        <is>
+          <t>is_pct</t>
+        </is>
+      </c>
+      <c r="L43" s="0" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="N43" s="0" t="inlineStr">
+        <is>
+          <t>true=百分比, false=固定值</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="0" t="inlineStr">
+        <is>
+          <t>common.BuffConfigRow</t>
+        </is>
+      </c>
+      <c r="E44" s="0" t="inlineStr">
+        <is>
+          <t>c,s,e</t>
+        </is>
+      </c>
+      <c r="G44" s="0" t="inlineStr">
+        <is>
+          <t>Buff配置行</t>
+        </is>
+      </c>
+      <c r="J44" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L44" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N44" s="0" t="inlineStr">
+        <is>
+          <t>Buff ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="J45" s="0" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="L45" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N45" s="0" t="inlineStr">
+        <is>
+          <t>Buff名称</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="J46" s="0" t="inlineStr">
+        <is>
+          <t>buff_type</t>
+        </is>
+      </c>
+      <c r="L46" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N46" s="0" t="inlineStr">
+        <is>
+          <t>Buff/Debuff</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="J47" s="0" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="L47" s="0" t="inlineStr">
+        <is>
+          <t>(list#sep=|),string</t>
+        </is>
+      </c>
+      <c r="N47" s="0" t="inlineStr">
+        <is>
+          <t>标签: stun/dot/shield等</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="J48" s="0" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="L48" s="0" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="N48" s="0" t="inlineStr">
+        <is>
+          <t>持续时间(秒), 0=即时</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="J49" s="0" t="inlineStr">
+        <is>
+          <t>max_stacks</t>
+        </is>
+      </c>
+      <c r="L49" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N49" s="0" t="inlineStr">
+        <is>
+          <t>最大叠加层数</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="J50" s="0" t="inlineStr">
+        <is>
+          <t>stack_rule</t>
+        </is>
+      </c>
+      <c r="L50" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N50" s="0" t="inlineStr">
+        <is>
+          <t>叠加规则: Refresh/Add/Ignore</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="J51" s="0" t="inlineStr">
+        <is>
+          <t>tick_interval</t>
+        </is>
+      </c>
+      <c r="L51" s="0" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="N51" s="0" t="inlineStr">
+        <is>
+          <t>Tick间隔(秒), 0=不tick</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="J52" s="0" t="inlineStr">
+        <is>
+          <t>effects</t>
+        </is>
+      </c>
+      <c r="L52" s="0" t="inlineStr">
+        <is>
+          <t>(list#sep=|),common.BuffEffectBean</t>
+        </is>
+      </c>
+      <c r="N52" s="0" t="inlineStr">
+        <is>
+          <t>效果列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="J53" s="0" t="inlineStr">
+        <is>
+          <t>attr_modifiers</t>
+        </is>
+      </c>
+      <c r="L53" s="0" t="inlineStr">
+        <is>
+          <t>(list#sep=|),common.BuffAttrModifierBean</t>
+        </is>
+      </c>
+      <c r="N53" s="0" t="inlineStr">
+        <is>
+          <t>属性修正列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="J54" s="0" t="inlineStr">
+        <is>
+          <t>shield_base</t>
+        </is>
+      </c>
+      <c r="L54" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N54" s="0" t="inlineStr">
+        <is>
+          <t>吸收盾基础值（0=非盾）</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>clear_on_disengage</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>脱战时是否清除</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="0" t="inlineStr">
+        <is>
+          <t>common.CombatLogTextRow</t>
+        </is>
+      </c>
+      <c r="E56" s="0" t="inlineStr">
+        <is>
+          <t>c,s,e</t>
+        </is>
+      </c>
+      <c r="G56" s="0" t="inlineStr">
+        <is>
+          <t>战斗日志文本行</t>
+        </is>
+      </c>
+      <c r="J56" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L56" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N56" s="0" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="J57" s="0" t="inlineStr">
+        <is>
+          <t>template</t>
+        </is>
+      </c>
+      <c r="L57" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N57" s="0" t="inlineStr">
+        <is>
+          <t>文本模板</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="J58" s="0" t="inlineStr">
+        <is>
+          <t>color</t>
+        </is>
+      </c>
+      <c r="L58" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N58" s="0" t="inlineStr">
+        <is>
+          <t>显示颜色</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="0" t="inlineStr">
+        <is>
+          <t>common.SkillConfigRow</t>
+        </is>
+      </c>
+      <c r="E59" s="0" t="inlineStr">
+        <is>
+          <t>c,s,e</t>
+        </is>
+      </c>
+      <c r="G59" s="0" t="inlineStr">
+        <is>
+          <t>技能配置行</t>
+        </is>
+      </c>
+      <c r="J59" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L59" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N59" s="0" t="inlineStr">
+        <is>
+          <t>技能ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="J60" s="0" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="L60" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N60" s="0" t="inlineStr">
+        <is>
+          <t>技能名称</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="J61" s="0" t="inlineStr">
+        <is>
+          <t>cast_range</t>
+        </is>
+      </c>
+      <c r="L61" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N61" s="0" t="inlineStr">
+        <is>
+          <t>施法距离</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="J62" s="0" t="inlineStr">
+        <is>
+          <t>cast_time</t>
+        </is>
+      </c>
+      <c r="L62" s="0" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="N62" s="0" t="inlineStr">
+        <is>
+          <t>施法时间(秒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="J63" s="0" t="inlineStr">
+        <is>
+          <t>interrupt_on_move</t>
+        </is>
+      </c>
+      <c r="L63" s="0" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="N63" s="0" t="inlineStr">
+        <is>
+          <t>移动打断</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="J64" s="0" t="inlineStr">
+        <is>
+          <t>post_cast_time</t>
+        </is>
+      </c>
+      <c r="L64" s="0" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="N64" s="0" t="inlineStr">
+        <is>
+          <t>后摇时间(秒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="J65" s="0" t="inlineStr">
+        <is>
+          <t>cooldown</t>
+        </is>
+      </c>
+      <c r="L65" s="0" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="N65" s="0" t="inlineStr">
+        <is>
+          <t>冷却时间(秒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="J66" s="0" t="inlineStr">
+        <is>
+          <t>mp_cost</t>
+        </is>
+      </c>
+      <c r="L66" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N66" s="0" t="inlineStr">
+        <is>
+          <t>MP消耗</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="J67" s="0" t="inlineStr">
+        <is>
+          <t>target_type</t>
+        </is>
+      </c>
+      <c r="L67" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N67" s="0" t="inlineStr">
+        <is>
+          <t>目标类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="J68" s="0" t="inlineStr">
+        <is>
+          <t>actions</t>
+        </is>
+      </c>
+      <c r="L68" s="0" t="inlineStr">
+        <is>
+          <t>(list#sep=|),common.CombatActionBean</t>
+        </is>
+      </c>
+      <c r="N68" s="0" t="inlineStr">
+        <is>
+          <t>动作列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="J69" s="0" t="inlineStr">
+        <is>
+          <t>job</t>
+        </is>
+      </c>
+      <c r="L69" s="0" t="inlineStr">
+        <is>
+          <t>common.EJobType</t>
+        </is>
+      </c>
+      <c r="N69" s="0" t="inlineStr">
+        <is>
+          <t>所属职业</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="0" t="inlineStr">
+        <is>
+          <t>common.PlayerAttrCfg</t>
+        </is>
+      </c>
+      <c r="E70" s="0" t="inlineStr">
+        <is>
+          <t>c,s,e</t>
+        </is>
+      </c>
+      <c r="G70" s="0" t="inlineStr">
+        <is>
+          <t>玩家属性配置</t>
+        </is>
+      </c>
+      <c r="J70" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L70" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N70" s="0" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="J71" s="0" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="L71" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N71" s="0" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="J72" s="0" t="inlineStr">
+        <is>
+          <t>mp</t>
+        </is>
+      </c>
+      <c r="L72" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N72" s="0" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="J73" s="0" t="inlineStr">
+        <is>
+          <t>agility</t>
+        </is>
+      </c>
+      <c r="L73" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N73" s="0" t="inlineStr">
+        <is>
+          <t>敏捷</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="J74" s="0" t="inlineStr">
+        <is>
+          <t>patk</t>
+        </is>
+      </c>
+      <c r="L74" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N74" s="0" t="inlineStr">
+        <is>
+          <t>物攻</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="J75" s="0" t="inlineStr">
+        <is>
+          <t>matk</t>
+        </is>
+      </c>
+      <c r="L75" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N75" s="0" t="inlineStr">
+        <is>
+          <t>魔攻</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="J76" s="0" t="inlineStr">
+        <is>
+          <t>pdef</t>
+        </is>
+      </c>
+      <c r="L76" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N76" s="0" t="inlineStr">
+        <is>
+          <t>物防</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="J77" s="0" t="inlineStr">
+        <is>
+          <t>mdef</t>
+        </is>
+      </c>
+      <c r="L77" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N77" s="0" t="inlineStr">
+        <is>
+          <t>魔防</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="J78" s="0" t="inlineStr">
+        <is>
+          <t>move_speed</t>
+        </is>
+      </c>
+      <c r="L78" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N78" s="0" t="inlineStr">
+        <is>
+          <t>移动速度(ms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="J79" s="0" t="inlineStr">
+        <is>
+          <t>mp_regen</t>
+        </is>
+      </c>
+      <c r="L79" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N79" s="0" t="inlineStr">
+        <is>
+          <t>每秒MP恢复量</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="0" t="inlineStr">
+        <is>
+          <t>common.LevelUpRow</t>
+        </is>
+      </c>
+      <c r="E80" s="0" t="inlineStr">
+        <is>
+          <t>c,s,e</t>
+        </is>
+      </c>
+      <c r="G80" s="0" t="inlineStr">
+        <is>
+          <t>升级表行</t>
+        </is>
+      </c>
+      <c r="J80" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L80" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N80" s="0" t="inlineStr">
+        <is>
+          <t>等级</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="J81" s="0" t="inlineStr">
+        <is>
+          <t>exp_required</t>
+        </is>
+      </c>
+      <c r="L81" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N81" s="0" t="inlineStr">
+        <is>
+          <t>升到下一级所需累计经验</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="J82" s="0" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="L82" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N82" s="0" t="inlineStr">
+        <is>
+          <t>HP加成</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="J83" s="0" t="inlineStr">
+        <is>
+          <t>mp</t>
+        </is>
+      </c>
+      <c r="L83" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N83" s="0" t="inlineStr">
+        <is>
+          <t>MP加成</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="J84" s="0" t="inlineStr">
+        <is>
+          <t>patk</t>
+        </is>
+      </c>
+      <c r="L84" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N84" s="0" t="inlineStr">
+        <is>
+          <t>物攻加成</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="J85" s="0" t="inlineStr">
+        <is>
+          <t>matk</t>
+        </is>
+      </c>
+      <c r="L85" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N85" s="0" t="inlineStr">
+        <is>
+          <t>魔攻加成</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="J86" s="0" t="inlineStr">
+        <is>
+          <t>pdef</t>
+        </is>
+      </c>
+      <c r="L86" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N86" s="0" t="inlineStr">
+        <is>
+          <t>物防加成</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="J87" s="0" t="inlineStr">
+        <is>
+          <t>mdef</t>
+        </is>
+      </c>
+      <c r="L87" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N87" s="0" t="inlineStr">
+        <is>
+          <t>魔防加成</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="J88" s="0" t="inlineStr">
+        <is>
+          <t>agility</t>
+        </is>
+      </c>
+      <c r="L88" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N88" s="0" t="inlineStr">
+        <is>
+          <t>敏捷加成</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="0" t="inlineStr">
+        <is>
+          <t>common.DropEntry</t>
+        </is>
+      </c>
+      <c r="E89" s="0" t="inlineStr">
+        <is>
+          <t>c,s,e</t>
+        </is>
+      </c>
+      <c r="F89" s="0" t="inlineStr">
+        <is>
+          <t>,</t>
+        </is>
+      </c>
+      <c r="G89" s="0" t="inlineStr">
+        <is>
+          <t>掉落条目</t>
+        </is>
+      </c>
+      <c r="J89" s="0" t="inlineStr">
+        <is>
+          <t>item_id</t>
+        </is>
+      </c>
+      <c r="L89" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N89" s="0" t="inlineStr">
+        <is>
+          <t>物品ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="J90" s="0" t="inlineStr">
+        <is>
+          <t>count_min</t>
+        </is>
+      </c>
+      <c r="L90" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N90" s="0" t="inlineStr">
+        <is>
+          <t>最小数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="J91" s="0" t="inlineStr">
+        <is>
+          <t>count_max</t>
+        </is>
+      </c>
+      <c r="L91" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N91" s="0" t="inlineStr">
+        <is>
+          <t>最大数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="J92" s="0" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="L92" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N92" s="0" t="inlineStr">
+        <is>
+          <t>权重</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="J93" s="0" t="inlineStr">
+        <is>
+          <t>guaranteed</t>
+        </is>
+      </c>
+      <c r="L93" s="0" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="N93" s="0" t="inlineStr">
+        <is>
+          <t>是否必掉</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" s="0" t="inlineStr">
+        <is>
+          <t>common.DropGroupRow</t>
+        </is>
+      </c>
+      <c r="E94" s="0" t="inlineStr">
+        <is>
+          <t>c,s,e</t>
+        </is>
+      </c>
+      <c r="F94" s="0" t="inlineStr">
+        <is>
+          <t>,</t>
+        </is>
+      </c>
+      <c r="G94" s="0" t="inlineStr">
+        <is>
+          <t>掉落组配置</t>
+        </is>
+      </c>
+      <c r="J94" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L94" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N94" s="0" t="inlineStr">
+        <is>
+          <t>掉落组ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="J95" s="0" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="L95" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N95" s="0" t="inlineStr">
+        <is>
+          <t>掉落组名称</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="J96" s="0" t="inlineStr">
+        <is>
+          <t>entries</t>
+        </is>
+      </c>
+      <c r="L96" s="0" t="inlineStr">
+        <is>
+          <t>(list#sep=|),common.DropEntry</t>
+        </is>
+      </c>
+      <c r="N96" s="0" t="inlineStr">
+        <is>
+          <t>掉落条目列表</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J1:P1"/>

--- a/tables/datas/__beans__.xlsx
+++ b/tables/datas/__beans__.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P96"/>
+  <dimension ref="A1:P98"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.625" customWidth="1" style="4" min="2" max="2"/>
@@ -1599,17 +1599,17 @@
       </c>
     </row>
     <row r="55">
-      <c r="J55" t="inlineStr">
+      <c r="J55" s="0" t="inlineStr">
         <is>
           <t>clear_on_disengage</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="L55" s="0" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="N55" s="0" t="inlineStr">
         <is>
           <t>脱战时是否清除</t>
         </is>
@@ -1884,75 +1884,75 @@
       </c>
     </row>
     <row r="70">
-      <c r="B70" s="0" t="inlineStr">
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>projectile_speed</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>弹道飞行速度(格/秒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>projectile_max_range</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>弹道最大飞行距离(格)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="0" t="inlineStr">
         <is>
           <t>common.PlayerAttrCfg</t>
         </is>
       </c>
-      <c r="E70" s="0" t="inlineStr">
+      <c r="E72" s="0" t="inlineStr">
         <is>
           <t>c,s,e</t>
         </is>
       </c>
-      <c r="G70" s="0" t="inlineStr">
+      <c r="G72" s="0" t="inlineStr">
         <is>
           <t>玩家属性配置</t>
         </is>
       </c>
-      <c r="J70" s="0" t="inlineStr">
+      <c r="J72" s="0" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="L70" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N70" s="0" t="inlineStr">
+      <c r="L72" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N72" s="0" t="inlineStr">
         <is>
           <t>ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="J71" s="0" t="inlineStr">
-        <is>
-          <t>hp</t>
-        </is>
-      </c>
-      <c r="L71" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N71" s="0" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="J72" s="0" t="inlineStr">
-        <is>
-          <t>mp</t>
-        </is>
-      </c>
-      <c r="L72" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N72" s="0" t="inlineStr">
-        <is>
-          <t>MP</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="J73" s="0" t="inlineStr">
         <is>
-          <t>agility</t>
+          <t>hp</t>
         </is>
       </c>
       <c r="L73" s="0" t="inlineStr">
@@ -1962,14 +1962,14 @@
       </c>
       <c r="N73" s="0" t="inlineStr">
         <is>
-          <t>敏捷</t>
+          <t>HP</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="J74" s="0" t="inlineStr">
         <is>
-          <t>patk</t>
+          <t>mp</t>
         </is>
       </c>
       <c r="L74" s="0" t="inlineStr">
@@ -1979,14 +1979,14 @@
       </c>
       <c r="N74" s="0" t="inlineStr">
         <is>
-          <t>物攻</t>
+          <t>MP</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="J75" s="0" t="inlineStr">
         <is>
-          <t>matk</t>
+          <t>agility</t>
         </is>
       </c>
       <c r="L75" s="0" t="inlineStr">
@@ -1996,14 +1996,14 @@
       </c>
       <c r="N75" s="0" t="inlineStr">
         <is>
-          <t>魔攻</t>
+          <t>敏捷</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="J76" s="0" t="inlineStr">
         <is>
-          <t>pdef</t>
+          <t>patk</t>
         </is>
       </c>
       <c r="L76" s="0" t="inlineStr">
@@ -2013,14 +2013,14 @@
       </c>
       <c r="N76" s="0" t="inlineStr">
         <is>
-          <t>物防</t>
+          <t>物攻</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="J77" s="0" t="inlineStr">
         <is>
-          <t>mdef</t>
+          <t>matk</t>
         </is>
       </c>
       <c r="L77" s="0" t="inlineStr">
@@ -2030,14 +2030,14 @@
       </c>
       <c r="N77" s="0" t="inlineStr">
         <is>
-          <t>魔防</t>
+          <t>魔攻</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="J78" s="0" t="inlineStr">
         <is>
-          <t>move_speed</t>
+          <t>pdef</t>
         </is>
       </c>
       <c r="L78" s="0" t="inlineStr">
@@ -2047,14 +2047,14 @@
       </c>
       <c r="N78" s="0" t="inlineStr">
         <is>
-          <t>移动速度(ms)</t>
+          <t>物防</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="J79" s="0" t="inlineStr">
         <is>
-          <t>mp_regen</t>
+          <t>mdef</t>
         </is>
       </c>
       <c r="L79" s="0" t="inlineStr">
@@ -2064,29 +2064,14 @@
       </c>
       <c r="N79" s="0" t="inlineStr">
         <is>
-          <t>每秒MP恢复量</t>
+          <t>魔防</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="B80" s="0" t="inlineStr">
-        <is>
-          <t>common.LevelUpRow</t>
-        </is>
-      </c>
-      <c r="E80" s="0" t="inlineStr">
-        <is>
-          <t>c,s,e</t>
-        </is>
-      </c>
-      <c r="G80" s="0" t="inlineStr">
-        <is>
-          <t>升级表行</t>
-        </is>
-      </c>
       <c r="J80" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>move_speed</t>
         </is>
       </c>
       <c r="L80" s="0" t="inlineStr">
@@ -2096,14 +2081,14 @@
       </c>
       <c r="N80" s="0" t="inlineStr">
         <is>
-          <t>等级</t>
+          <t>移动速度(ms)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="J81" s="0" t="inlineStr">
         <is>
-          <t>exp_required</t>
+          <t>mp_regen</t>
         </is>
       </c>
       <c r="L81" s="0" t="inlineStr">
@@ -2113,14 +2098,29 @@
       </c>
       <c r="N81" s="0" t="inlineStr">
         <is>
-          <t>升到下一级所需累计经验</t>
+          <t>每秒MP恢复量</t>
         </is>
       </c>
     </row>
     <row r="82">
+      <c r="B82" s="0" t="inlineStr">
+        <is>
+          <t>common.LevelUpRow</t>
+        </is>
+      </c>
+      <c r="E82" s="0" t="inlineStr">
+        <is>
+          <t>c,s,e</t>
+        </is>
+      </c>
+      <c r="G82" s="0" t="inlineStr">
+        <is>
+          <t>升级表行</t>
+        </is>
+      </c>
       <c r="J82" s="0" t="inlineStr">
         <is>
-          <t>hp</t>
+          <t>id</t>
         </is>
       </c>
       <c r="L82" s="0" t="inlineStr">
@@ -2130,14 +2130,14 @@
       </c>
       <c r="N82" s="0" t="inlineStr">
         <is>
-          <t>HP加成</t>
+          <t>等级</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="J83" s="0" t="inlineStr">
         <is>
-          <t>mp</t>
+          <t>exp_required</t>
         </is>
       </c>
       <c r="L83" s="0" t="inlineStr">
@@ -2147,14 +2147,14 @@
       </c>
       <c r="N83" s="0" t="inlineStr">
         <is>
-          <t>MP加成</t>
+          <t>升到下一级所需累计经验</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="J84" s="0" t="inlineStr">
         <is>
-          <t>patk</t>
+          <t>hp</t>
         </is>
       </c>
       <c r="L84" s="0" t="inlineStr">
@@ -2164,14 +2164,14 @@
       </c>
       <c r="N84" s="0" t="inlineStr">
         <is>
-          <t>物攻加成</t>
+          <t>HP加成</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="J85" s="0" t="inlineStr">
         <is>
-          <t>matk</t>
+          <t>mp</t>
         </is>
       </c>
       <c r="L85" s="0" t="inlineStr">
@@ -2181,14 +2181,14 @@
       </c>
       <c r="N85" s="0" t="inlineStr">
         <is>
-          <t>魔攻加成</t>
+          <t>MP加成</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="J86" s="0" t="inlineStr">
         <is>
-          <t>pdef</t>
+          <t>patk</t>
         </is>
       </c>
       <c r="L86" s="0" t="inlineStr">
@@ -2198,14 +2198,14 @@
       </c>
       <c r="N86" s="0" t="inlineStr">
         <is>
-          <t>物防加成</t>
+          <t>物攻加成</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="J87" s="0" t="inlineStr">
         <is>
-          <t>mdef</t>
+          <t>matk</t>
         </is>
       </c>
       <c r="L87" s="0" t="inlineStr">
@@ -2215,14 +2215,14 @@
       </c>
       <c r="N87" s="0" t="inlineStr">
         <is>
-          <t>魔防加成</t>
+          <t>魔攻加成</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="J88" s="0" t="inlineStr">
         <is>
-          <t>agility</t>
+          <t>pdef</t>
         </is>
       </c>
       <c r="L88" s="0" t="inlineStr">
@@ -2232,34 +2232,14 @@
       </c>
       <c r="N88" s="0" t="inlineStr">
         <is>
-          <t>敏捷加成</t>
+          <t>物防加成</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="0" t="inlineStr">
-        <is>
-          <t>common.DropEntry</t>
-        </is>
-      </c>
-      <c r="E89" s="0" t="inlineStr">
-        <is>
-          <t>c,s,e</t>
-        </is>
-      </c>
-      <c r="F89" s="0" t="inlineStr">
-        <is>
-          <t>,</t>
-        </is>
-      </c>
-      <c r="G89" s="0" t="inlineStr">
-        <is>
-          <t>掉落条目</t>
-        </is>
-      </c>
       <c r="J89" s="0" t="inlineStr">
         <is>
-          <t>item_id</t>
+          <t>mdef</t>
         </is>
       </c>
       <c r="L89" s="0" t="inlineStr">
@@ -2269,14 +2249,14 @@
       </c>
       <c r="N89" s="0" t="inlineStr">
         <is>
-          <t>物品ID</t>
+          <t>魔防加成</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="J90" s="0" t="inlineStr">
         <is>
-          <t>count_min</t>
+          <t>agility</t>
         </is>
       </c>
       <c r="L90" s="0" t="inlineStr">
@@ -2286,14 +2266,34 @@
       </c>
       <c r="N90" s="0" t="inlineStr">
         <is>
-          <t>最小数量</t>
+          <t>敏捷加成</t>
         </is>
       </c>
     </row>
     <row r="91">
+      <c r="B91" s="0" t="inlineStr">
+        <is>
+          <t>common.DropEntry</t>
+        </is>
+      </c>
+      <c r="E91" s="0" t="inlineStr">
+        <is>
+          <t>c,s,e</t>
+        </is>
+      </c>
+      <c r="F91" s="0" t="inlineStr">
+        <is>
+          <t>,</t>
+        </is>
+      </c>
+      <c r="G91" s="0" t="inlineStr">
+        <is>
+          <t>掉落条目</t>
+        </is>
+      </c>
       <c r="J91" s="0" t="inlineStr">
         <is>
-          <t>count_max</t>
+          <t>item_id</t>
         </is>
       </c>
       <c r="L91" s="0" t="inlineStr">
@@ -2303,14 +2303,14 @@
       </c>
       <c r="N91" s="0" t="inlineStr">
         <is>
-          <t>最大数量</t>
+          <t>物品ID</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="J92" s="0" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>count_min</t>
         </is>
       </c>
       <c r="L92" s="0" t="inlineStr">
@@ -2320,51 +2320,31 @@
       </c>
       <c r="N92" s="0" t="inlineStr">
         <is>
-          <t>权重</t>
+          <t>最小数量</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="J93" s="0" t="inlineStr">
         <is>
-          <t>guaranteed</t>
+          <t>count_max</t>
         </is>
       </c>
       <c r="L93" s="0" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>int</t>
         </is>
       </c>
       <c r="N93" s="0" t="inlineStr">
         <is>
-          <t>是否必掉</t>
+          <t>最大数量</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="B94" s="0" t="inlineStr">
-        <is>
-          <t>common.DropGroupRow</t>
-        </is>
-      </c>
-      <c r="E94" s="0" t="inlineStr">
-        <is>
-          <t>c,s,e</t>
-        </is>
-      </c>
-      <c r="F94" s="0" t="inlineStr">
-        <is>
-          <t>,</t>
-        </is>
-      </c>
-      <c r="G94" s="0" t="inlineStr">
-        <is>
-          <t>掉落组配置</t>
-        </is>
-      </c>
       <c r="J94" s="0" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>weight</t>
         </is>
       </c>
       <c r="L94" s="0" t="inlineStr">
@@ -2374,39 +2354,93 @@
       </c>
       <c r="N94" s="0" t="inlineStr">
         <is>
-          <t>掉落组ID</t>
+          <t>权重</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="J95" s="0" t="inlineStr">
         <is>
+          <t>guaranteed</t>
+        </is>
+      </c>
+      <c r="L95" s="0" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="N95" s="0" t="inlineStr">
+        <is>
+          <t>是否必掉</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="0" t="inlineStr">
+        <is>
+          <t>common.DropGroupRow</t>
+        </is>
+      </c>
+      <c r="E96" s="0" t="inlineStr">
+        <is>
+          <t>c,s,e</t>
+        </is>
+      </c>
+      <c r="F96" s="0" t="inlineStr">
+        <is>
+          <t>,</t>
+        </is>
+      </c>
+      <c r="G96" s="0" t="inlineStr">
+        <is>
+          <t>掉落组配置</t>
+        </is>
+      </c>
+      <c r="J96" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L96" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N96" s="0" t="inlineStr">
+        <is>
+          <t>掉落组ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="J97" s="0" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
-      <c r="L95" s="0" t="inlineStr">
+      <c r="L97" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N95" s="0" t="inlineStr">
+      <c r="N97" s="0" t="inlineStr">
         <is>
           <t>掉落组名称</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="J96" s="0" t="inlineStr">
+    <row r="98">
+      <c r="J98" s="0" t="inlineStr">
         <is>
           <t>entries</t>
         </is>
       </c>
-      <c r="L96" s="0" t="inlineStr">
+      <c r="L98" s="0" t="inlineStr">
         <is>
           <t>(list#sep=|),common.DropEntry</t>
         </is>
       </c>
-      <c r="N96" s="0" t="inlineStr">
+      <c r="N98" s="0" t="inlineStr">
         <is>
           <t>掉落条目列表</t>
         </is>

--- a/tables/datas/__beans__.xlsx
+++ b/tables/datas/__beans__.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P98"/>
+  <dimension ref="A1:P103"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.625" customWidth="1" style="4" min="2" max="2"/>
@@ -810,6 +810,8 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14"/>
     <row r="15">
       <c r="B15" s="0" t="inlineStr">
         <is>
@@ -1059,6 +1061,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="B28" s="0" t="inlineStr">
         <is>
@@ -1884,34 +1887,34 @@
       </c>
     </row>
     <row r="70">
-      <c r="J70" t="inlineStr">
+      <c r="J70" s="0" t="inlineStr">
         <is>
           <t>projectile_speed</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="L70" s="0" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
+      <c r="N70" s="0" t="inlineStr">
         <is>
           <t>弹道飞行速度(格/秒)</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="J71" t="inlineStr">
+      <c r="J71" s="0" t="inlineStr">
         <is>
           <t>projectile_max_range</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
+      <c r="L71" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N71" s="0" t="inlineStr">
         <is>
           <t>弹道最大飞行距离(格)</t>
         </is>
@@ -2443,6 +2446,116 @@
       <c r="N98" s="0" t="inlineStr">
         <is>
           <t>掉落条目列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="J99" s="0" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="L99" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M99" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="N99" s="0" t="inlineStr">
+        <is>
+          <t>章节标题</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="J100" s="0" t="inlineStr">
+        <is>
+          <t>chapter_id</t>
+        </is>
+      </c>
+      <c r="L100" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="M100" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="N100" s="0" t="inlineStr">
+        <is>
+          <t>所属章节ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="J101" s="0" t="inlineStr">
+        <is>
+          <t>sequence</t>
+        </is>
+      </c>
+      <c r="L101" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="M101" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="N101" s="0" t="inlineStr">
+        <is>
+          <t>章节内顺序</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="J102" s="0" t="inlineStr">
+        <is>
+          <t>speaker</t>
+        </is>
+      </c>
+      <c r="L102" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M102" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="N102" s="0" t="inlineStr">
+        <is>
+          <t>说话人，空表示旁白</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="J103" s="0" t="inlineStr">
+        <is>
+          <t>content</t>
+        </is>
+      </c>
+      <c r="L103" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M103" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="N103" s="0" t="inlineStr">
+        <is>
+          <t>文本内容</t>
         </is>
       </c>
     </row>
